--- a/config/xlsx/initial_setup.xlsx
+++ b/config/xlsx/initial_setup.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>

--- a/config/xlsx/initial_setup.xlsx
+++ b/config/xlsx/initial_setup.xlsx
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>501</v>
+        <v>11001</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>504</v>
+        <v>12001</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
@@ -525,13 +525,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>601</v>
+        <v>13001</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>602</v>
+        <v>14001</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>603</v>
+        <v>15001</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>506</v>
+        <v>16001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
@@ -609,17 +609,17 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>21</v>
+        <v>17001</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -630,17 +630,17 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>22</v>
+        <v>18001</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>23</v>
+        <v>19001</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
@@ -672,31 +672,31 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>24</v>
+        <v>20001</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>FALSE</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>battle</t>
+          <t>main</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>505</v>
+        <v>21001</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>4</v>

--- a/config/xlsx/initial_setup.xlsx
+++ b/config/xlsx/initial_setup.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -483,17 +483,17 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>11001</v>
+        <v>11002</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -504,17 +504,17 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>12001</v>
+        <v>12002</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -525,17 +525,17 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13001</v>
+        <v>11003</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -546,17 +546,17 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>14001</v>
+        <v>12003</v>
       </c>
       <c r="C5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -567,17 +567,17 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>15001</v>
+        <v>11001</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -588,17 +588,17 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>16001</v>
+        <v>12001</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>17001</v>
+        <v>11001</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
@@ -630,17 +630,17 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>18001</v>
+        <v>5001</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -651,17 +651,17 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>19001</v>
+        <v>5002</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>20001</v>
+        <v>5003</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>FALSE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -693,17 +693,101 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>21001</v>
+        <v>5004</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>9001</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>9002</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>9003</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>FALSE</t>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>9004</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
     </row>

--- a/config/xlsx/initial_setup.xlsx
+++ b/config/xlsx/initial_setup.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -791,6 +791,69 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>17001</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>16001</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
